--- a/data/trans_orig/IP25A02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35798</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64417</t>
+          <t>64803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>28557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44768</t>
+          <t>44315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>38986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>64254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97937</t>
+          <t>97769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98115</t>
+          <t>98832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136541</t>
+          <t>135425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172970</t>
+          <t>172050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223194</t>
+          <t>221021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139622</t>
+          <t>141137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196945</t>
+          <t>196619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187181</t>
+          <t>186658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235754</t>
+          <t>234423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349151</t>
+          <t>347832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419096</t>
+          <t>419053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138378</t>
+          <t>139480</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228483</t>
+          <t>218051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135666</t>
+          <t>137312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188381</t>
+          <t>190985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>289205</t>
+          <t>289201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>381395</t>
+          <t>383615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35320</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>47631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54001</t>
+          <t>52899</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79309</t>
+          <t>79034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>62433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113539</t>
+          <t>110445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143664</t>
+          <t>141748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64366</t>
+          <t>64223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>47438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71439</t>
+          <t>71498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>99371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129401</t>
+          <t>129129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>60985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>65771</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118309</t>
+          <t>117298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103067</t>
+          <t>101510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144027</t>
+          <t>143304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146619</t>
+          <t>145773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189452</t>
+          <t>188250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>262315</t>
+          <t>258035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322343</t>
+          <t>319937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222340</t>
+          <t>222179</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>281750</t>
+          <t>283336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>281039</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>335667</t>
+          <t>337426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>518143</t>
+          <t>526371</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>603579</t>
+          <t>605431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198893</t>
+          <t>200503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>284214</t>
+          <t>286244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205142</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262559</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419990</t>
+          <t>419056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525355</t>
+          <t>523174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8890</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4689</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14908</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2563</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6586</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13474</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20355</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13063</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23986</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23439</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16567</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29957</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>41,66%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26356</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17356</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32451</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41290</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64803</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10455</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9038</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14738</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25021</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17130</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35909</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31808</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>22370</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44315</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59480</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76825</t>
+          <t>68671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>111722</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93381</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>129083</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>81370</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64254</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97769</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>116530</t>
+          <t>82454</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98832</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135425</t>
+          <t>94725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>197901</t>
+          <t>194176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172050</t>
+          <t>173382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>198216</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>221759</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>176846</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141137</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>196619</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209978</t>
+          <t>177099</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186658</t>
+          <t>160471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234423</t>
+          <t>195942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>386824</t>
+          <t>375315</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347832</t>
+          <t>348423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419053</t>
+          <t>402970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138265</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>121205</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164039</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>163647</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>139480</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>218051</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159838</t>
+          <t>136685</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137312</t>
+          <t>118957</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190985</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>323485</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>289201</t>
+          <t>251700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383615</t>
+          <t>309520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>453671</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>453671</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>453671</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425530</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>967691</t>
+          <t>898754</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>967691</t>
+          <t>898754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>967691</t>
+          <t>898754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8054</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22879</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11254</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18030</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35798</t>
+          <t>35423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32912</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24521</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>43409</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29352</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>22278</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>37919</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65233</t>
+          <t>62851</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79034</t>
+          <t>74693</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>69641</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58027</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81069</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>53509</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43525</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>62433</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>53679</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62025</t>
+          <t>44027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>127314</t>
+          <t>123320</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110445</t>
+          <t>108879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141748</t>
+          <t>138163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>52148</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42905</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63375</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>54357</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>45695</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>64223</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59155</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>44791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71498</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>105812</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99371</t>
+          <t>92059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129129</t>
+          <t>119636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>47629</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>36319</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>61615</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>45624</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>35005</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>60985</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>76212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117298</t>
+          <t>107977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>158108</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>137594</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>179232</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>123786</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>101510</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>143304</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,94%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>166507</t>
+          <t>123561</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145773</t>
+          <t>107967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188250</t>
+          <t>141242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>290293</t>
+          <t>281669</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>258035</t>
+          <t>256759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>319937</t>
+          <t>308597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>291296</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>266619</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>314806</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>362</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>256711</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>222179</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>283336</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>34,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>309313</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>228436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>337426</t>
+          <t>270559</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>566024</t>
+          <t>542231</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526371</t>
+          <t>508704</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>605431</t>
+          <t>573059</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>200868</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>180845</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>228946</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>227042</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>200503</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>286244</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>30,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>230524</t>
+          <t>199680</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>179109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>400548</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419056</t>
+          <t>370950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523174</t>
+          <t>433668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>653163</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>653163</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>653163</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617912</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1411958</t>
+          <t>1315813</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1411958</t>
+          <t>1315813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1411958</t>
+          <t>1315813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
